--- a/Mentoria_Emerson_13082026/01_PLANILHA_COMPARATIVA_PESQUISAS.xlsx
+++ b/Mentoria_Emerson_13082026/01_PLANILHA_COMPARATIVA_PESQUISAS.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,6 +53,16 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00404040"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -125,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -176,6 +186,8 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2983,7 +2995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3409,6 +3421,101 @@
       <c r="E17" s="18" t="inlineStr">
         <is>
           <t>Perplexidade caiu 49% mas a classificação DEGRADOU. Com 352 exemplos; a literatura usa 1.500.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>ONDE OUTRAS PESQUISAS NOS SUPERAM — comparação legítima</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Halousková e Lyócsa (2025) — previsão de volatilidade</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>vencem o HAR em 98,76% dos casos</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>nós NÃO vencemos (p=0,64)</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Seção 4.k e 4.m</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>Comparável: mesmo alvo, mesma referência, fora da amostra. Eles usam 404 ativos e variância de 5 min; nós, 1 ativo e Parkinson diário.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Bodilsen e Lunde (2025) — previsão de volatilidade</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>melhora significativa sobre a família HAR</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>não superamos com recorte algum</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Seção 4.o</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Comparável. A receita específica (macro &gt; empresa) inverte-se na PETR4, mas o resultado deles permanece superior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Electronics (2025), art. 4680 — classificação</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>F1-macro de 0,707 com 1.500 rótulos</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>F1-macro de 0,579 com 352</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Seção 4.m</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>Comparável: mesma tarefa. A diferença é volume de supervisão.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>LEITURA: esta pesquisa não apresenta o melhor desempenho do conjunto levantado. Apresenta a avaliação mais rigorosa. São méritos distintos.</t>
         </is>
       </c>
     </row>
